--- a/ipc_mensual.xlsx
+++ b/ipc_mensual.xlsx
@@ -802,7 +802,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>0.7109742776312586</v>
+        <v>0.6493855198117898</v>
       </c>
       <c r="C2" s="2">
         <v>42370</v>
@@ -813,7 +813,7 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>0.7387022744588783</v>
+        <v>0.6747115550844501</v>
       </c>
       <c r="C3" s="2">
         <v>42401</v>
@@ -824,7 +824,7 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>0.7675116631627767</v>
+        <v>0.7010253057327457</v>
       </c>
       <c r="C4" s="2">
         <v>42430</v>
@@ -835,7 +835,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>0.7928395480471483</v>
+        <v>0.7241591408219262</v>
       </c>
       <c r="C5" s="2">
         <v>42461</v>
@@ -846,7 +846,7 @@
         <v>7</v>
       </c>
       <c r="B6">
-        <v>0.8419956000260665</v>
+        <v>0.7690570075528812</v>
       </c>
       <c r="C6" s="2">
         <v>42491</v>
@@ -857,7 +857,7 @@
         <v>8</v>
       </c>
       <c r="B7">
-        <v>0.8773038435175646</v>
+        <v>0.8013066441076082</v>
       </c>
       <c r="C7" s="2">
         <v>42522</v>
@@ -868,7 +868,7 @@
         <v>9</v>
       </c>
       <c r="B8">
-        <v>0.9042881185071956</v>
+        <v>0.8259533830856589</v>
       </c>
       <c r="C8" s="2">
         <v>42552</v>
@@ -879,7 +879,7 @@
         <v>10</v>
       </c>
       <c r="B9">
-        <v>0.9227968657869721</v>
+        <v>0.8428587942256895</v>
       </c>
       <c r="C9" s="2">
         <v>42583</v>
@@ -890,7 +890,7 @@
         <v>11</v>
       </c>
       <c r="B10">
-        <v>0.9246610440454225</v>
+        <v>0.844561486440405</v>
       </c>
       <c r="C10" s="2">
         <v>42614</v>
@@ -901,7 +901,7 @@
         <v>12</v>
       </c>
       <c r="B11">
-        <v>0.9352861865221531</v>
+        <v>0.8542662168187163</v>
       </c>
       <c r="C11" s="2">
         <v>42644</v>
@@ -912,7 +912,7 @@
         <v>13</v>
       </c>
       <c r="B12">
-        <v>0.9573532072076359</v>
+        <v>0.8744216628726619</v>
       </c>
       <c r="C12" s="2">
         <v>42675</v>
@@ -923,7 +923,7 @@
         <v>14</v>
       </c>
       <c r="B13">
-        <v>0.9728476102393225</v>
+        <v>0.8885738499256562</v>
       </c>
       <c r="C13" s="2">
         <v>42705</v>
@@ -934,7 +934,7 @@
         <v>15</v>
       </c>
       <c r="B14">
-        <v>0.9844974613612827</v>
+        <v>0.8992145226821574</v>
       </c>
       <c r="C14" s="2">
         <v>42736</v>
@@ -945,7 +945,7 @@
         <v>16</v>
       </c>
       <c r="B15">
-        <v>1.000110606601006</v>
+        <v>0.9134751657973688</v>
       </c>
       <c r="C15" s="2">
         <v>42767</v>
@@ -956,7 +956,7 @@
         <v>17</v>
       </c>
       <c r="B16">
-        <v>1.02078505328959</v>
+        <v>0.9323586707736914</v>
       </c>
       <c r="C16" s="2">
         <v>42795</v>
@@ -967,7 +967,7 @@
         <v>18</v>
       </c>
       <c r="B17">
-        <v>1.045020427295924</v>
+        <v>0.9544946346785614</v>
       </c>
       <c r="C17" s="2">
         <v>42826</v>
@@ -978,7 +978,7 @@
         <v>19</v>
       </c>
       <c r="B18">
-        <v>1.072774395229157</v>
+        <v>0.9798443912874915</v>
       </c>
       <c r="C18" s="2">
         <v>42856</v>
@@ -989,7 +989,7 @@
         <v>20</v>
       </c>
       <c r="B19">
-        <v>1.088166028540087</v>
+        <v>0.9939027111351113</v>
       </c>
       <c r="C19" s="2">
         <v>42887</v>
@@ -1000,7 +1000,7 @@
         <v>21</v>
       </c>
       <c r="B20">
-        <v>1.101137767090979</v>
+        <v>1.005750761685968</v>
       </c>
       <c r="C20" s="2">
         <v>42917</v>
@@ -1011,7 +1011,7 @@
         <v>22</v>
       </c>
       <c r="B21">
-        <v>1.120212405404857</v>
+        <v>1.023173043062937</v>
       </c>
       <c r="C21" s="2">
         <v>42948</v>
@@ -1022,7 +1022,7 @@
         <v>23</v>
       </c>
       <c r="B22">
-        <v>1.135931876370404</v>
+        <v>1.037530801346596</v>
       </c>
       <c r="C22" s="2">
         <v>42979</v>
@@ -1033,7 +1033,7 @@
         <v>24</v>
       </c>
       <c r="B23">
-        <v>1.15749237077423</v>
+        <v>1.057223599393347</v>
       </c>
       <c r="C23" s="2">
         <v>43009</v>
@@ -1044,7 +1044,7 @@
         <v>25</v>
       </c>
       <c r="B24">
-        <v>1.175025286063611</v>
+        <v>1.073237710827792</v>
       </c>
       <c r="C24" s="2">
         <v>43040</v>
@@ -1055,7 +1055,7 @@
         <v>26</v>
       </c>
       <c r="B25">
-        <v>1.191182858399466</v>
+        <v>1.087995619574045</v>
       </c>
       <c r="C25" s="2">
         <v>43070</v>
@@ -1066,7 +1066,7 @@
         <v>27</v>
       </c>
       <c r="B26">
-        <v>1.228609513890581</v>
+        <v>1.122180158868335</v>
       </c>
       <c r="C26" s="2">
         <v>43101</v>
@@ -1077,7 +1077,7 @@
         <v>28</v>
       </c>
       <c r="B27">
-        <v>1.250200527715685</v>
+        <v>1.141900832565267</v>
       </c>
       <c r="C27" s="2">
         <v>43132</v>
@@ -1088,7 +1088,7 @@
         <v>29</v>
       </c>
       <c r="B28">
-        <v>1.280443305231247</v>
+        <v>1.169523803487545</v>
       </c>
       <c r="C28" s="2">
         <v>43160</v>
@@ -1099,7 +1099,7 @@
         <v>30</v>
       </c>
       <c r="B29">
-        <v>1.310419283934776</v>
+        <v>1.196903087274171</v>
       </c>
       <c r="C29" s="2">
         <v>43191</v>
@@ -1110,7 +1110,7 @@
         <v>31</v>
       </c>
       <c r="B30">
-        <v>1.346312092381085</v>
+        <v>1.229686650342118</v>
       </c>
       <c r="C30" s="2">
         <v>43221</v>
@@ -1121,7 +1121,7 @@
         <v>32</v>
       </c>
       <c r="B31">
-        <v>1.374253114831983</v>
+        <v>1.255207257710363</v>
       </c>
       <c r="C31" s="2">
         <v>43252</v>
@@ -1132,7 +1132,7 @@
         <v>33</v>
       </c>
       <c r="B32">
-        <v>1.42560450241658</v>
+        <v>1.302110287213458</v>
       </c>
       <c r="C32" s="2">
         <v>43282</v>
@@ -1143,7 +1143,7 @@
         <v>34</v>
       </c>
       <c r="B33">
-        <v>1.469821236898701</v>
+        <v>1.342496709070682</v>
       </c>
       <c r="C33" s="2">
         <v>43313</v>
@@ -1154,7 +1154,7 @@
         <v>35</v>
       </c>
       <c r="B34">
-        <v>1.526989035485037</v>
+        <v>1.394712297973798</v>
       </c>
       <c r="C34" s="2">
         <v>43344</v>
@@ -1165,7 +1165,7 @@
         <v>36</v>
       </c>
       <c r="B35">
-        <v>1.626766868696527</v>
+        <v>1.4858467906331</v>
       </c>
       <c r="C35" s="2">
         <v>43374</v>
@@ -1176,7 +1176,7 @@
         <v>37</v>
       </c>
       <c r="B36">
-        <v>1.714475747529209</v>
+        <v>1.565957812458858</v>
       </c>
       <c r="C36" s="2">
         <v>43405</v>
@@ -1187,7 +1187,7 @@
         <v>38</v>
       </c>
       <c r="B37">
-        <v>1.768539425619863</v>
+        <v>1.615338177971947</v>
       </c>
       <c r="C37" s="2">
         <v>43435</v>
@@ -1198,7 +1198,7 @@
         <v>39</v>
       </c>
       <c r="B38">
-        <v>1.813987766426148</v>
+        <v>1.656849517197048</v>
       </c>
       <c r="C38" s="2">
         <v>43466</v>
@@ -1209,7 +1209,7 @@
         <v>40</v>
       </c>
       <c r="B39">
-        <v>1.866706620984579</v>
+        <v>1.705001555672152</v>
       </c>
       <c r="C39" s="2">
         <v>43497</v>
@@ -1220,7 +1220,7 @@
         <v>41</v>
       </c>
       <c r="B40">
-        <v>1.93699973972577</v>
+        <v>1.769205472591654</v>
       </c>
       <c r="C40" s="2">
         <v>43525</v>
@@ -1231,7 +1231,7 @@
         <v>42</v>
       </c>
       <c r="B41">
-        <v>2.027642420993307</v>
+        <v>1.851996153695004</v>
       </c>
       <c r="C41" s="2">
         <v>43556</v>
@@ -1242,7 +1242,7 @@
         <v>43</v>
       </c>
       <c r="B42">
-        <v>2.097488577887046</v>
+        <v>1.915791827221213</v>
       </c>
       <c r="C42" s="2">
         <v>43586</v>
@@ -1253,7 +1253,7 @@
         <v>44</v>
       </c>
       <c r="B43">
-        <v>2.161652215433808</v>
+        <v>1.9743972345225</v>
       </c>
       <c r="C43" s="2">
         <v>43617</v>
@@ -1264,7 +1264,7 @@
         <v>45</v>
       </c>
       <c r="B44">
-        <v>2.220406039430394</v>
+        <v>2.028061458021655</v>
       </c>
       <c r="C44" s="2">
         <v>43647</v>
@@ -1275,7 +1275,7 @@
         <v>46</v>
       </c>
       <c r="B45">
-        <v>2.269207578590062</v>
+        <v>2.072635521911</v>
       </c>
       <c r="C45" s="2">
         <v>43678</v>
@@ -1286,7 +1286,7 @@
         <v>47</v>
       </c>
       <c r="B46">
-        <v>2.35893172372615</v>
+        <v>2.154587235864688</v>
       </c>
       <c r="C46" s="2">
         <v>43709</v>
@@ -1297,7 +1297,7 @@
         <v>48</v>
       </c>
       <c r="B47">
-        <v>2.497770478214628</v>
+        <v>2.281398963925942</v>
       </c>
       <c r="C47" s="2">
         <v>43739</v>
@@ -1308,7 +1308,7 @@
         <v>49</v>
       </c>
       <c r="B48">
-        <v>2.580034101588515</v>
+        <v>2.356536430226738</v>
       </c>
       <c r="C48" s="2">
         <v>43770</v>
@@ -1319,7 +1319,7 @@
         <v>50</v>
       </c>
       <c r="B49">
-        <v>2.689802615037908</v>
+        <v>2.456796151862227</v>
       </c>
       <c r="C49" s="2">
         <v>43800</v>
@@ -1330,7 +1330,7 @@
         <v>51</v>
       </c>
       <c r="B50">
-        <v>2.790500953375779</v>
+        <v>2.548771410100243</v>
       </c>
       <c r="C50" s="2">
         <v>43831</v>
@@ -1341,7 +1341,7 @@
         <v>52</v>
       </c>
       <c r="B51">
-        <v>2.853368007765929</v>
+        <v>2.606192551875159</v>
       </c>
       <c r="C51" s="2">
         <v>43862</v>
@@ -1352,7 +1352,7 @@
         <v>53</v>
       </c>
       <c r="B52">
-        <v>2.910824264108438</v>
+        <v>2.658671610633415</v>
       </c>
       <c r="C52" s="2">
         <v>43891</v>
@@ -1363,7 +1363,7 @@
         <v>54</v>
       </c>
       <c r="B53">
-        <v>3.008146760651306</v>
+        <v>2.747563462273159</v>
       </c>
       <c r="C53" s="2">
         <v>43922</v>
@@ -1374,7 +1374,7 @@
         <v>55</v>
       </c>
       <c r="B54">
-        <v>3.053165860564433</v>
+        <v>2.788682743966367</v>
       </c>
       <c r="C54" s="2">
         <v>43952</v>
@@ -1385,7 +1385,7 @@
         <v>56</v>
       </c>
       <c r="B55">
-        <v>3.100268157105807</v>
+        <v>2.831704763589577</v>
       </c>
       <c r="C55" s="2">
         <v>43983</v>
@@ -1396,7 +1396,7 @@
         <v>57</v>
       </c>
       <c r="B56">
-        <v>3.169823887248454</v>
+        <v>2.895235168831604</v>
       </c>
       <c r="C56" s="2">
         <v>44013</v>
@@ -1407,7 +1407,7 @@
         <v>58</v>
       </c>
       <c r="B57">
-        <v>3.23113445115218</v>
+        <v>2.95123465244615</v>
       </c>
       <c r="C57" s="2">
         <v>44044</v>
@@ -1418,7 +1418,7 @@
         <v>59</v>
       </c>
       <c r="B58">
-        <v>3.318378647183085</v>
+        <v>3.030921245017189</v>
       </c>
       <c r="C58" s="2">
         <v>44075</v>
@@ -1429,7 +1429,7 @@
         <v>60</v>
       </c>
       <c r="B59">
-        <v>3.412471992052697</v>
+        <v>3.116863673022543</v>
       </c>
       <c r="C59" s="2">
         <v>44105</v>
@@ -1440,7 +1440,7 @@
         <v>61</v>
       </c>
       <c r="B60">
-        <v>3.540814034608133</v>
+        <v>3.234087975842954</v>
       </c>
       <c r="C60" s="2">
         <v>44136</v>
@@ -1451,7 +1451,7 @@
         <v>62</v>
       </c>
       <c r="B61">
-        <v>3.652693310614691</v>
+        <v>3.336275613415077</v>
       </c>
       <c r="C61" s="2">
         <v>44166</v>
@@ -1462,7 +1462,7 @@
         <v>63</v>
       </c>
       <c r="B62">
-        <v>3.799004400834906</v>
+        <v>3.469912379703493</v>
       </c>
       <c r="C62" s="2">
         <v>44197</v>
@@ -1473,7 +1473,7 @@
         <v>64</v>
       </c>
       <c r="B63">
-        <v>3.952827206685292</v>
+        <v>3.610410152799958</v>
       </c>
       <c r="C63" s="2">
         <v>44228</v>
@@ -1484,7 +1484,7 @@
         <v>65</v>
       </c>
       <c r="B64">
-        <v>4.094126220329713</v>
+        <v>3.739469017953396</v>
       </c>
       <c r="C64" s="2">
         <v>44256</v>
@@ -1495,7 +1495,7 @@
         <v>66</v>
       </c>
       <c r="B65">
-        <v>4.291086751444571</v>
+        <v>3.919367673790232</v>
       </c>
       <c r="C65" s="2">
         <v>44287</v>
@@ -1506,7 +1506,7 @@
         <v>67</v>
       </c>
       <c r="B66">
-        <v>4.466175686957832</v>
+        <v>4.079289379791164</v>
       </c>
       <c r="C66" s="2">
         <v>44317</v>
@@ -1517,7 +1517,7 @@
         <v>68</v>
       </c>
       <c r="B67">
-        <v>4.614585725765657</v>
+        <v>4.214843271441928</v>
       </c>
       <c r="C67" s="2">
         <v>44348</v>
@@ -1528,7 +1528,7 @@
         <v>69</v>
       </c>
       <c r="B68">
-        <v>4.761077963518756</v>
+        <v>4.34864549320251</v>
       </c>
       <c r="C68" s="2">
         <v>44378</v>
@@ -1539,7 +1539,7 @@
         <v>70</v>
       </c>
       <c r="B69">
-        <v>4.903769056573535</v>
+        <v>4.478975847691014</v>
       </c>
       <c r="C69" s="2">
         <v>44409</v>
@@ -1550,7 +1550,7 @@
         <v>71</v>
       </c>
       <c r="B70">
-        <v>5.024817941935217</v>
+        <v>4.589538769327404</v>
       </c>
       <c r="C70" s="2">
         <v>44440</v>
@@ -1561,7 +1561,7 @@
         <v>72</v>
       </c>
       <c r="B71">
-        <v>5.203037579375601</v>
+        <v>4.752319977510461</v>
       </c>
       <c r="C71" s="2">
         <v>44470</v>
@@ -1572,7 +1572,7 @@
         <v>73</v>
       </c>
       <c r="B72">
-        <v>5.385990680610218</v>
+        <v>4.919424609118581</v>
       </c>
       <c r="C72" s="2">
         <v>44501</v>
@@ -1583,7 +1583,7 @@
         <v>74</v>
       </c>
       <c r="B73">
-        <v>5.522227408308308</v>
+        <v>5.043859713196377</v>
       </c>
       <c r="C73" s="2">
         <v>44531</v>
@@ -1594,7 +1594,7 @@
         <v>75</v>
       </c>
       <c r="B74">
-        <v>5.734279301008373</v>
+        <v>5.237542428451406</v>
       </c>
       <c r="C74" s="2">
         <v>44562</v>
@@ -1605,7 +1605,7 @@
         <v>76</v>
       </c>
       <c r="B75">
-        <v>5.956521726930996</v>
+        <v>5.440532913230726</v>
       </c>
       <c r="C75" s="2">
         <v>44593</v>
@@ -1616,7 +1616,7 @@
         <v>77</v>
       </c>
       <c r="B76">
-        <v>6.23614263389667</v>
+        <v>5.695931418821001</v>
       </c>
       <c r="C76" s="2">
         <v>44621</v>
@@ -1627,7 +1627,7 @@
         <v>78</v>
       </c>
       <c r="B77">
-        <v>6.655760064365382</v>
+        <v>6.079199128751203</v>
       </c>
       <c r="C77" s="2">
         <v>44652</v>
@@ -1638,7 +1638,7 @@
         <v>79</v>
       </c>
       <c r="B78">
-        <v>7.058255114986099</v>
+        <v>6.446827699702917</v>
       </c>
       <c r="C78" s="2">
         <v>44682</v>
@@ -1649,7 +1649,7 @@
         <v>80</v>
       </c>
       <c r="B79">
-        <v>7.414713095318652</v>
+        <v>6.77240720114498</v>
       </c>
       <c r="C79" s="2">
         <v>44713</v>
@@ -1660,7 +1660,7 @@
         <v>81</v>
       </c>
       <c r="B80">
-        <v>7.807338558889185</v>
+        <v>7.131021146506772</v>
       </c>
       <c r="C80" s="2">
         <v>44743</v>
@@ -1671,7 +1671,7 @@
         <v>82</v>
       </c>
       <c r="B81">
-        <v>8.385565421865502</v>
+        <v>7.659158610542795</v>
       </c>
       <c r="C81" s="2">
         <v>44774</v>
@@ -1682,7 +1682,7 @@
         <v>83</v>
       </c>
       <c r="B82">
-        <v>8.970067471660427</v>
+        <v>8.193027667946293</v>
       </c>
       <c r="C82" s="2">
         <v>44805</v>
@@ -1693,7 +1693,7 @@
         <v>84</v>
       </c>
       <c r="B83">
-        <v>9.52311876555464</v>
+        <v>8.698170418208131</v>
       </c>
       <c r="C83" s="2">
         <v>44835</v>
@@ -1704,7 +1704,7 @@
         <v>85</v>
       </c>
       <c r="B84">
-        <v>10.12758445487116</v>
+        <v>9.250273747702678</v>
       </c>
       <c r="C84" s="2">
         <v>44866</v>
@@ -1715,7 +1715,7 @@
         <v>86</v>
       </c>
       <c r="B85">
-        <v>10.62547140251303</v>
+        <v>9.705030810615169</v>
       </c>
       <c r="C85" s="2">
         <v>44896</v>
@@ -1726,7 +1726,7 @@
         <v>87</v>
       </c>
       <c r="B86">
-        <v>11.16998513442242</v>
+        <v>10.2023755725364</v>
       </c>
       <c r="C86" s="2">
         <v>44927</v>
@@ -1737,7 +1737,7 @@
         <v>88</v>
       </c>
       <c r="B87">
-        <v>11.8432977157093</v>
+        <v>10.81736187281655</v>
       </c>
       <c r="C87" s="2">
         <v>44958</v>
@@ -1748,7 +1748,7 @@
         <v>89</v>
       </c>
       <c r="B88">
-        <v>12.62823852615008</v>
+        <v>11.53430651096551</v>
       </c>
       <c r="C88" s="2">
         <v>44986</v>
@@ -1759,7 +1759,7 @@
         <v>90</v>
       </c>
       <c r="B89">
-        <v>13.59748612183485</v>
+        <v>12.41959220069132</v>
       </c>
       <c r="C89" s="2">
         <v>45017</v>
@@ -1770,7 +1770,7 @@
         <v>91</v>
       </c>
       <c r="B90">
-        <v>14.74004071262787</v>
+        <v>13.46317201813202</v>
       </c>
       <c r="C90" s="2">
         <v>45047</v>
@@ -1781,7 +1781,7 @@
         <v>92</v>
       </c>
       <c r="B91">
-        <v>15.88976388821289</v>
+        <v>14.51329943554638</v>
       </c>
       <c r="C91" s="2">
         <v>45078</v>
@@ -1792,7 +1792,7 @@
         <v>93</v>
       </c>
       <c r="B92">
-        <v>16.84314972150565</v>
+        <v>15.38409740167914</v>
       </c>
       <c r="C92" s="2">
         <v>45108</v>
@@ -1803,7 +1803,7 @@
         <v>94</v>
       </c>
       <c r="B93">
-        <v>17.90426815396053</v>
+        <v>16.35329553798494</v>
       </c>
       <c r="C93" s="2">
         <v>45139</v>
@@ -1814,7 +1814,7 @@
         <v>95</v>
       </c>
       <c r="B94">
-        <v>20.12439740505166</v>
+        <v>18.3811041846951</v>
       </c>
       <c r="C94" s="2">
         <v>45170</v>
@@ -1825,7 +1825,7 @@
         <v>96</v>
       </c>
       <c r="B95">
-        <v>22.68019587549315</v>
+        <v>20.71550441615133</v>
       </c>
       <c r="C95" s="2">
         <v>45200</v>
@@ -1836,7 +1836,7 @@
         <v>97</v>
       </c>
       <c r="B96">
-        <v>24.56265213315915</v>
+        <v>22.43489128269195</v>
       </c>
       <c r="C96" s="2">
         <v>45231</v>
@@ -1847,7 +1847,7 @@
         <v>98</v>
       </c>
       <c r="B97">
-        <v>27.7066716062035</v>
+        <v>25.30655736687649</v>
       </c>
       <c r="C97" s="2">
         <v>45261</v>
@@ -1858,7 +1858,7 @@
         <v>99</v>
       </c>
       <c r="B98">
-        <v>34.77187286578541</v>
+        <v>31.75972949543002</v>
       </c>
       <c r="C98" s="2">
         <v>45292</v>
@@ -1869,7 +1869,7 @@
         <v>100</v>
       </c>
       <c r="B99">
-        <v>41.93487867613715</v>
+        <v>38.30223377148856</v>
       </c>
       <c r="C99" s="2">
         <v>45323</v>
@@ -1880,7 +1880,7 @@
         <v>101</v>
       </c>
       <c r="B100">
-        <v>47.47028266138729</v>
+        <v>43.35812862932507</v>
       </c>
       <c r="C100" s="2">
         <v>45352</v>
@@ -1891,7 +1891,7 @@
         <v>102</v>
       </c>
       <c r="B101">
-        <v>52.69201375413989</v>
+        <v>48.12752277855084</v>
       </c>
       <c r="C101" s="2">
         <v>45383</v>
@@ -1902,7 +1902,7 @@
         <v>103</v>
       </c>
       <c r="B102">
-        <v>57.32891096450422</v>
+        <v>52.36274478306333</v>
       </c>
       <c r="C102" s="2">
         <v>45413</v>
@@ -1913,7 +1913,7 @@
         <v>104</v>
       </c>
       <c r="B103">
-        <v>59.73672522501344</v>
+        <v>54.56198006395201</v>
       </c>
       <c r="C103" s="2">
         <v>45444</v>
@@ -1924,7 +1924,7 @@
         <v>105</v>
       </c>
       <c r="B104">
-        <v>62.48461458536404</v>
+        <v>57.07183114689379</v>
       </c>
       <c r="C104" s="2">
         <v>45474</v>
@@ -1935,7 +1935,7 @@
         <v>106</v>
       </c>
       <c r="B105">
-        <v>64.98399916877858</v>
+        <v>59.35470439276952</v>
       </c>
       <c r="C105" s="2">
         <v>45505</v>
@@ -1946,7 +1946,7 @@
         <v>107</v>
       </c>
       <c r="B106">
-        <v>67.84329513220486</v>
+        <v>61.96631138605139</v>
       </c>
       <c r="C106" s="2">
         <v>45536</v>
@@ -1957,7 +1957,7 @@
         <v>108</v>
       </c>
       <c r="B107">
-        <v>70.21781046183204</v>
+        <v>64.13513228456321</v>
       </c>
       <c r="C107" s="2">
         <v>45566</v>
@@ -1968,7 +1968,7 @@
         <v>109</v>
       </c>
       <c r="B108">
-        <v>72.46478039661071</v>
+        <v>66.18745651766926</v>
       </c>
       <c r="C108" s="2">
         <v>45597</v>
@@ -1979,7 +1979,7 @@
         <v>110</v>
       </c>
       <c r="B109">
-        <v>74.20393512612931</v>
+        <v>67.77595547409328</v>
       </c>
       <c r="C109" s="2">
         <v>45627</v>
@@ -1990,7 +1990,7 @@
         <v>111</v>
       </c>
       <c r="B110">
-        <v>76.05903350428254</v>
+        <v>69.47035436094561</v>
       </c>
       <c r="C110" s="2">
         <v>45658</v>
@@ -2001,7 +2001,7 @@
         <v>112</v>
       </c>
       <c r="B111">
-        <v>77.73233224137675</v>
+        <v>70.99870215688641</v>
       </c>
       <c r="C111" s="2">
         <v>45689</v>
@@ -2012,7 +2012,7 @@
         <v>113</v>
       </c>
       <c r="B112">
-        <v>79.5979082151698</v>
+        <v>72.70267100865169</v>
       </c>
       <c r="C112" s="2">
         <v>45717</v>
@@ -2023,7 +2023,7 @@
         <v>114</v>
       </c>
       <c r="B113">
-        <v>82.54303081913108</v>
+        <v>75.3926698359718</v>
       </c>
       <c r="C113" s="2">
         <v>45748</v>
@@ -2034,7 +2034,7 @@
         <v>115</v>
       </c>
       <c r="B114">
-        <v>84.85423568206674</v>
+        <v>77.50366459137901</v>
       </c>
       <c r="C114" s="2">
         <v>45778</v>
@@ -2045,7 +2045,7 @@
         <v>116</v>
       </c>
       <c r="B115">
-        <v>86.12704921729774</v>
+        <v>78.66621956024969</v>
       </c>
       <c r="C115" s="2">
         <v>45809</v>
@@ -2056,7 +2056,7 @@
         <v>117</v>
       </c>
       <c r="B116">
-        <v>87.50508200477451</v>
+        <v>79.92487907321369</v>
       </c>
       <c r="C116" s="2">
         <v>45839</v>
@@ -2067,7 +2067,7 @@
         <v>118</v>
       </c>
       <c r="B117">
-        <v>89.16767856286522</v>
+        <v>81.44345177560474</v>
       </c>
       <c r="C117" s="2">
         <v>45870</v>
@@ -2078,7 +2078,7 @@
         <v>119</v>
       </c>
       <c r="B118">
-        <v>90.86186445555965</v>
+        <v>82.99087735934123</v>
       </c>
       <c r="C118" s="2">
         <v>45901</v>
@@ -2089,7 +2089,7 @@
         <v>120</v>
       </c>
       <c r="B119">
-        <v>92.76996360912639</v>
+        <v>84.73368578388738</v>
       </c>
       <c r="C119" s="2">
         <v>45931</v>
@@ -2100,7 +2100,7 @@
         <v>121</v>
       </c>
       <c r="B120">
-        <v>94.90367277213629</v>
+        <v>86.68256055691678</v>
       </c>
       <c r="C120" s="2">
         <v>45962</v>
@@ -2111,7 +2111,7 @@
         <v>122</v>
       </c>
       <c r="B121">
-        <v>97.27626459143968</v>
+        <v>88.84962457083969</v>
       </c>
       <c r="C121" s="2">
         <v>45992</v>
@@ -2122,7 +2122,7 @@
         <v>123</v>
       </c>
       <c r="B122">
-        <v>100</v>
+        <v>91.33741405882321</v>
       </c>
       <c r="C122" s="2">
         <v>46023</v>
@@ -2133,7 +2133,7 @@
         <v>124</v>
       </c>
       <c r="B123">
-        <v>100</v>
+        <v>93.98619906652908</v>
       </c>
       <c r="C123" s="2">
         <v>46054</v>
@@ -2144,7 +2144,7 @@
         <v>125</v>
       </c>
       <c r="B124">
-        <v>100</v>
+        <v>96.71179883945841</v>
       </c>
       <c r="C124" s="2">
         <v>46082</v>
